--- a/AOC metrics.xlsx
+++ b/AOC metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Code\AOC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C5FE114-A371-4A46-956A-DE0EA740575A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706D08D7-C071-496F-8CC0-604058D7C229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{5D288D66-0459-47EC-A889-AF44D9CD3BA9}"/>
   </bookViews>
@@ -87,7 +87,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -209,33 +209,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
@@ -327,7 +311,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -341,7 +325,15 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Problem 1</c:v>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>problem 1 time</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -355,97 +347,13 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$B$2:$B$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
                   <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -465,6 +373,60 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>98</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -472,7 +434,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6385-43E1-B218-4D2E37C191D7}"/>
+              <c16:uniqueId val="{00000002-1AD9-4F93-99F4-069201AA2932}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -480,7 +442,15 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>Problem 2</c:v>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>problem 2 time</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -494,97 +464,13 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
-          <c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$26</c:f>
+              <c:f>Sheet1!$C$2:$C$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>13</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>25</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$C$2:$C$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
                   <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -604,6 +490,60 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -611,7 +551,124 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-6385-43E1-B218-4D2E37C191D7}"/>
+              <c16:uniqueId val="{00000003-1AD9-4F93-99F4-069201AA2932}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>total time </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1AD9-4F93-99F4-069201AA2932}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -686,7 +743,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1851,16 +1908,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1973,19 +2030,27 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="B9" s="1">
+        <v>98</v>
+      </c>
+      <c r="C9" s="1">
+        <v>44</v>
+      </c>
       <c r="D9" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
       <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1995,8 +2060,12 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
       <c r="D11" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2006,8 +2075,12 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2017,8 +2090,12 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
       <c r="D13" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2028,8 +2105,12 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="B14" s="1">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2039,8 +2120,12 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
       <c r="D15" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2050,8 +2135,12 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
       <c r="D16" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2061,8 +2150,12 @@
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0</v>
+      </c>
       <c r="D17" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2072,8 +2165,12 @@
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2083,8 +2180,12 @@
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
       <c r="D19" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2094,8 +2195,12 @@
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0</v>
+      </c>
       <c r="D20" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2105,8 +2210,12 @@
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
       <c r="D21" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2116,8 +2225,12 @@
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0</v>
+      </c>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2127,8 +2240,12 @@
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0</v>
+      </c>
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2138,8 +2255,12 @@
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
+      <c r="B24" s="1">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2149,8 +2270,12 @@
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
+      <c r="B25" s="1">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0</v>
+      </c>
       <c r="D25" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2160,8 +2285,12 @@
       <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0</v>
+      </c>
       <c r="D26" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
